--- a/IaR_GaR_April_2026/Outputs/wis/wis_skewt_gdp_OOS.xlsx
+++ b/IaR_GaR_April_2026/Outputs/wis/wis_skewt_gdp_OOS.xlsx
@@ -94,7 +94,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>0.92450120494682231</v>
+        <v>0.9240951400137114</v>
       </c>
     </row>
   </sheetData>
